--- a/outputs/516-46.xlsx
+++ b/outputs/516-46.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="14">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -164,15 +164,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -432,7 +432,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -464,7 +464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>43831</v>
       </c>
@@ -481,26 +481,22 @@
         <v>10</v>
       </c>
       <c r="H2" s="3" t="n">
-        <f aca="false">_xlfn.MAXIFS($A$2:$A$8,$B$2:$B$8,I2)</f>
         <v>43832</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="1" t="str">
-        <f aca="false">INDEX($C$2:$C$8,MATCH(1,($B$2:$B$8=I2)*($A$2:$A$8=H2),0))</f>
-        <v>ca-1001</v>
-      </c>
-      <c r="K2" s="1" t="str">
-        <f aca="false">INDEX($D$2:$D$8,MATCH(1,($B$2:$B$8=I2)*($A$2:$A$8=H2),0))</f>
-        <v>chi</v>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="L2" s="1" t="n">
-        <f aca="false">SUMIFS($E$2:$E$8,$B$2:$B$8,I2,$A$2:$A$8,H2)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
         <v>43832</v>
       </c>
@@ -517,26 +513,22 @@
         <v>20</v>
       </c>
       <c r="H3" s="3" t="n">
-        <f aca="false">_xlfn.MAXIFS($A$2:$A$8,$B$2:$B$8,I3)</f>
         <v>43835</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="1" t="str">
-        <f aca="false">INDEX($C$2:$C$8,MATCH(1,($B$2:$B$8=I3)*($A$2:$A$8=H3),0))</f>
-        <v>ca-1002</v>
-      </c>
-      <c r="K3" s="1" t="str">
-        <f aca="false">INDEX($D$2:$D$8,MATCH(1,($B$2:$B$8=I3)*($A$2:$A$8=H3),0))</f>
-        <v>eur</v>
+      <c r="J3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="L3" s="1" t="n">
-        <f aca="false">SUMIFS($E$2:$E$8,$B$2:$B$8,I3,$A$2:$A$8,H3)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
         <v>43833</v>
       </c>
@@ -553,26 +545,22 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <f aca="false">_xlfn.MAXIFS($A$2:$A$8,$B$2:$B$8,I4)</f>
         <v>43837</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="1" t="str">
-        <f aca="false">INDEX($C$2:$C$8,MATCH(1,($B$2:$B$8=I4)*($A$2:$A$8=H4),0))</f>
-        <v>ca-1003</v>
-      </c>
-      <c r="K4" s="1" t="str">
-        <f aca="false">INDEX($D$2:$D$8,MATCH(1,($B$2:$B$8=I4)*($A$2:$A$8=H4),0))</f>
-        <v>thi</v>
+      <c r="J4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="L4" s="1" t="n">
-        <f aca="false">SUMIFS($E$2:$E$8,$B$2:$B$8,I4,$A$2:$A$8,H4)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
         <v>43834</v>
       </c>
@@ -589,7 +577,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
         <v>43835</v>
       </c>
@@ -606,7 +594,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
         <v>43836</v>
       </c>
@@ -623,7 +611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
         <v>43837</v>
       </c>

--- a/outputs/516-46.xlsx
+++ b/outputs/516-46.xlsx
@@ -46,6 +46,15 @@
     <t xml:space="preserve">chi</t>
   </si>
   <si>
+    <t xml:space="preserve">scanner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca-1003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thi</t>
+  </si>
+  <si>
     <t xml:space="preserve">film</t>
   </si>
   <si>
@@ -53,24 +62,16 @@
   </si>
   <si>
     <t xml:space="preserve">eur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scanner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca-1003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -159,7 +160,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -173,6 +174,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -425,7 +430,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.16"/>
@@ -483,17 +488,20 @@
       <c r="H2" s="3" t="n">
         <v>43832</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>5</v>
+      <c r="I2" s="4" t="n">
+        <v>43837</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="1" t="n">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -512,19 +520,20 @@
       <c r="E3" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="3"/>
+      <c r="I3" s="4" t="n">
         <v>43835</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="1" t="n">
         <v>12</v>
       </c>
     </row>
@@ -533,31 +542,32 @@
         <v>43833</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>43837</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>11</v>
+      <c r="H4" s="3"/>
+      <c r="I4" s="4" t="n">
+        <v>43832</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -565,13 +575,13 @@
         <v>43834</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>60</v>
@@ -582,13 +592,13 @@
         <v>43835</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>12</v>
@@ -599,13 +609,13 @@
         <v>43836</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>5</v>
@@ -616,13 +626,13 @@
         <v>43837</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>10</v>
